--- a/data/trans_dic/BARTHEL_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,44; 93,11</t>
+          <t>7,11; 12,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,6; 86,03</t>
+          <t>13,81; 22,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,21; 87,5</t>
+          <t>12,38; 19,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75,64; 83,28</t>
+          <t>16,85; 24,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,06; 88,69</t>
+          <t>11,33; 17,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,77; 76,08</t>
+          <t>23,86; 31,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,26; 78,47</t>
+          <t>21,84; 29,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,72; 72,57</t>
+          <t>27,4; 33,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,36; 89,69</t>
+          <t>10,51; 14,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,33; 79,11</t>
+          <t>20,73; 26,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75,19; 81,0</t>
+          <t>18,89; 24,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,61; 75,4</t>
+          <t>24,47; 29,37</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,26; 99,1</t>
+          <t>0,9; 8,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,61; 96,7</t>
+          <t>3,28; 12,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,68; 97,1</t>
+          <t>3,12; 9,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,86; 93,56</t>
+          <t>6,63; 12,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,38; 96,74</t>
+          <t>3,31; 17,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,4; 91,08</t>
+          <t>8,09; 24,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,54; 91,31</t>
+          <t>8,8; 19,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,76; 97,92</t>
+          <t>2,28; 13,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,02; 97,57</t>
+          <t>2,48; 9,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,45; 93,37</t>
+          <t>6,68; 15,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86,69; 93,36</t>
+          <t>6,36; 12,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,79; 96,65</t>
+          <t>3,39; 11,31</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,9; 100,0</t>
+          <t>0,0; 17,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,58; 100,0</t>
+          <t>0,0; 17,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,07; 98,14</t>
+          <t>1,86; 21,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,43; 97,16</t>
+          <t>2,5; 10,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,53; 96,47</t>
+          <t>3,5; 28,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,61; 95,58</t>
+          <t>4,51; 38,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,25; 100,0</t>
+          <t>0,0; 19,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,37; 96,2</t>
+          <t>3,68; 12,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,93; 98,26</t>
+          <t>1,94; 16,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80,22; 97,67</t>
+          <t>2,25; 20,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,48; 98,15</t>
+          <t>1,18; 14,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,66; 96,26</t>
+          <t>3,79; 9,45</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,41; 94,05</t>
+          <t>5,81; 10,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,53; 88,33</t>
+          <t>11,66; 18,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,25; 90,29</t>
+          <t>9,5; 14,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,76; 88,8</t>
+          <t>10,88; 15,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,03</t>
+          <t>10,84; 16,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,96; 77,52</t>
+          <t>22,49; 29,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,71; 81,57</t>
+          <t>18,5; 25,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,3; 90,22</t>
+          <t>9,7; 23,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,81; 90,5</t>
+          <t>9,31; 13,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,59; 81,23</t>
+          <t>18,66; 23,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,32; 84,58</t>
+          <t>15,4; 19,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,06; 89,98</t>
+          <t>10,36; 19,0</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1368,62 +1368,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>304</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>114</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>337189</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>339952</t>
+          <t>74446</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>56282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212910</t>
+          <t>54476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>505463</t>
+          <t>82286</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>461298</t>
+          <t>173247</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>412821</t>
+          <t>141936</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>345413</t>
+          <t>149688</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>842653</t>
+          <t>118285</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>801249</t>
+          <t>247693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>710440</t>
+          <t>198218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>558322</t>
+          <t>204164</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>326309; 347471</t>
+          <t>26516; 47574</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>321593; 356490</t>
+          <t>57219; 93393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>283865; 309656</t>
+          <t>43813; 70045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202246; 222680</t>
+          <t>45064; 65207</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>488199; 521271</t>
+          <t>66608; 101561</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>436353; 482766</t>
+          <t>151409; 196866</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>389780; 435345</t>
+          <t>121140; 164156</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>330309; 359279</t>
+          <t>135682; 164420</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>820276; 861842</t>
+          <t>100984; 139695</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>769170; 829778</t>
+          <t>217432; 275967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>683255; 736020</t>
+          <t>171638; 224066</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>538373; 574903</t>
+          <t>186616; 223941</t>
         </is>
       </c>
     </row>
@@ -1576,62 +1576,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -1644,62 +1644,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85636</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>110562</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181892</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248860</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70296</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>162636</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>424206</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>142399</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180858</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344529</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>673066</t>
+          <t>55583</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81261; 87290</t>
+          <t>797; 7576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>102770; 114753</t>
+          <t>3889; 15257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174587; 186955</t>
+          <t>6002; 17828</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>240081; 255673</t>
+          <t>18120; 32920</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50625; 60187</t>
+          <t>2059; 11049</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62638; 75666</t>
+          <t>6719; 20638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>149597; 171733</t>
+          <t>16552; 37217</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>395111; 445923</t>
+          <t>10362; 60520</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135292; 146639</t>
+          <t>3722; 14484</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170370; 188367</t>
+          <t>13476; 31086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>329932; 355318</t>
+          <t>24216; 48612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>646973; 704264</t>
+          <t>24712; 82415</t>
         </is>
       </c>
     </row>
@@ -1784,62 +1784,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1852,62 +1852,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39740</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>986</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63260</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44521</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71151</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>165403</t>
+          <t>10908</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32914; 41194</t>
+          <t>0; 7062</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20352; 26575</t>
+          <t>0; 4692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32811; 41247</t>
+          <t>780; 8875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93886; 102002</t>
+          <t>2626; 11180</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18421; 25932</t>
+          <t>940; 7678</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13928; 21262</t>
+          <t>1004; 8465</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27024; 33674</t>
+          <t>0; 6446</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62316; 68616</t>
+          <t>2627; 9203</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57138; 66891</t>
+          <t>1318; 11073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39167; 47686</t>
+          <t>1097; 10188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63955; 74302</t>
+          <t>891; 10906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>159850; 169711</t>
+          <t>6674; 16670</t>
         </is>
       </c>
     </row>
@@ -1992,62 +1992,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>383</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>522</t>
         </is>
       </c>
     </row>
@@ -2060,62 +2060,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>462565</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>476102</t>
+          <t>83535</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518365</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>561094</t>
+          <t>84534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>585747</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>550525</t>
+          <t>189340</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>607756</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>835696</t>
+          <t>186121</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1048312</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026627</t>
+          <t>272875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1126121</t>
+          <t>238847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1396790</t>
+          <t>270655</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>449238; 472568</t>
+          <t>29182; 52301</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>456251; 494339</t>
+          <t>65275; 101241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>501675; 531311</t>
+          <t>55918; 84730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>547257; 573335</t>
+          <t>70247; 98613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>565581; 602613</t>
+          <t>73382; 109071</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>524995; 573578</t>
+          <t>166415; 216209</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>580105; 633392</t>
+          <t>143689; 194142</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>779615; 921860</t>
+          <t>99120; 240901</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1023807; 1067262</t>
+          <t>109799; 153994</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>995319; 1055524</t>
+          <t>242545; 305102</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1096323; 1154535</t>
+          <t>210183; 266732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1351713; 1500353</t>
+          <t>172775; 316800</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/BARTHEL_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,75</t>
+          <t>7,06; 12,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 22,54</t>
+          <t>13,84; 22,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 19,79</t>
+          <t>12,43; 19,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 24,39</t>
+          <t>16,22; 23,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,28</t>
+          <t>11,36; 17,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 31,02</t>
+          <t>23,75; 30,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 29,59</t>
+          <t>21,92; 29,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,4; 33,21</t>
+          <t>27,68; 33,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 14,54</t>
+          <t>10,2; 14,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 26,31</t>
+          <t>20,87; 26,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,89; 24,66</t>
+          <t>19,32; 24,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,37</t>
+          <t>24,48; 29,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,6</t>
+          <t>0,88; 7,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,86</t>
+          <t>3,3; 13,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,26</t>
+          <t>3,15; 9,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,05</t>
+          <t>6,31; 11,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 17,76</t>
+          <t>3,19; 18,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 24,84</t>
+          <t>8,86; 25,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 19,79</t>
+          <t>8,77; 20,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,29</t>
+          <t>10,64; 16,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,64</t>
+          <t>2,52; 9,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,41</t>
+          <t>6,49; 15,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,77</t>
+          <t>6,72; 13,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,31</t>
+          <t>9,05; 13,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,14</t>
+          <t>0,0; 15,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,66</t>
+          <t>0,0; 16,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 21,12</t>
+          <t>1,84; 22,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 10,65</t>
+          <t>2,7; 10,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 28,56</t>
+          <t>3,46; 29,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 38,05</t>
+          <t>4,49; 36,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,14</t>
+          <t>0,0; 20,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,9</t>
+          <t>3,44; 11,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 16,27</t>
+          <t>1,85; 16,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,87</t>
+          <t>2,28; 21,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 14,41</t>
+          <t>1,78; 14,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,45</t>
+          <t>3,8; 9,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,41</t>
+          <t>6,2; 10,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,09</t>
+          <t>11,98; 18,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,4</t>
+          <t>9,6; 14,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,27</t>
+          <t>10,87; 14,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,11</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,49; 29,22</t>
+          <t>22,43; 28,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 25,0</t>
+          <t>18,7; 25,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 23,58</t>
+          <t>20,62; 24,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,06</t>
+          <t>9,36; 12,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,48</t>
+          <t>18,71; 23,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,4; 19,54</t>
+          <t>15,25; 19,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,0</t>
+          <t>16,93; 20,11</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>149688</t>
+          <t>162297</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>204164</t>
+          <t>219548</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26516; 47574</t>
+          <t>26336; 47375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57219; 93393</t>
+          <t>57342; 91265</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43813; 70045</t>
+          <t>43991; 69938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45064; 65207</t>
+          <t>46711; 68454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66608; 101561</t>
+          <t>66770; 100717</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151409; 196866</t>
+          <t>150716; 196636</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121140; 164156</t>
+          <t>121585; 165475</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135682; 164420</t>
+          <t>147487; 179491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100984; 139695</t>
+          <t>98038; 140042</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217432; 275967</t>
+          <t>218923; 277208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171638; 224066</t>
+          <t>175531; 224550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>186616; 223941</t>
+          <t>200980; 242123</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55583</t>
+          <t>62494</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>797; 7576</t>
+          <t>775; 6591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3889; 15257</t>
+          <t>3910; 16107</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6002; 17828</t>
+          <t>6068; 17794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18120; 32920</t>
+          <t>19168; 35743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2059; 11049</t>
+          <t>1982; 11325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6719; 20638</t>
+          <t>7359; 21111</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16552; 37217</t>
+          <t>16490; 39056</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10362; 60520</t>
+          <t>29518; 46147</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3722; 14484</t>
+          <t>3787; 14834</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13476; 31086</t>
+          <t>13093; 31629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24216; 48612</t>
+          <t>25559; 49914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24712; 82415</t>
+          <t>52589; 76222</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>12287</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7062</t>
+          <t>0; 6260</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4692</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>780; 8875</t>
+          <t>775; 9377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2626; 11180</t>
+          <t>3214; 12862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>940; 7678</t>
+          <t>930; 8015</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1004; 8465</t>
+          <t>1000; 8145</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6446</t>
+          <t>0; 6865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2627; 9203</t>
+          <t>2854; 9909</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1318; 11073</t>
+          <t>1258; 11270</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1097; 10188</t>
+          <t>1113; 10416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>891; 10906</t>
+          <t>1351; 11082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6674; 16670</t>
+          <t>7657; 19626</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>204552</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>270655</t>
+          <t>294329</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29182; 52301</t>
+          <t>31162; 53936</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65275; 101241</t>
+          <t>67035; 102984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55918; 84730</t>
+          <t>56480; 85265</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70247; 98613</t>
+          <t>77265; 105146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73382; 109071</t>
+          <t>75498; 111199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>166415; 216209</t>
+          <t>165925; 213176</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143689; 194142</t>
+          <t>145222; 196379</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99120; 240901</t>
+          <t>184180; 222619</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109799; 153994</t>
+          <t>110431; 153159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>242545; 305102</t>
+          <t>243090; 304591</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210183; 266732</t>
+          <t>208197; 267927</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>172775; 316800</t>
+          <t>271487; 322485</t>
         </is>
       </c>
     </row>
